--- a/datos_de_prueba/02_caso_con_problemas/PL-05_hoja_de_vida.xlsx
+++ b/datos_de_prueba/02_caso_con_problemas/PL-05_hoja_de_vida.xlsx
@@ -403,7 +403,7 @@
     <t>CHINA</t>
   </si>
   <si>
-    <t>2026-03-01</t>
+    <t>2030-03-01</t>
   </si>
   <si>
     <t>FV-2</t>
